--- a/app/reporting/cdm_reports/02_logistics_segment_92.2%_Fidelity.xlsx
+++ b/app/reporting/cdm_reports/02_logistics_segment_92.2%_Fidelity.xlsx
@@ -764,7 +764,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-02 11:20</t>
+          <t>SAP PD (PowerDesigner CDM) → erwin  |  Conceptual Model Validation Report   |   generated 2026-09-04 16:52</t>
         </is>
       </c>
     </row>
